--- a/output7/【河洛文讀注音-閩拼調號】《般若波羅蜜多心經》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調號】《般若波羅蜜多心經》.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4229E26-7F09-46DD-A3F2-38BB92A789D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B3BE711-D451-4954-8DDB-245C4B2FCCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24960" yWindow="0" windowWidth="25080" windowHeight="12270" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
+    <workbookView xWindow="28680" yWindow="-195" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{33AB2257-ECDF-4521-8F0E-4FD5B627422C}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="10" r:id="rId1"/>
@@ -2656,6 +2656,1451 @@
     <t>方音符號</t>
   </si>
   <si>
+    <t>無預設</t>
+  </si>
+  <si>
+    <t>kuan1</t>
+  </si>
+  <si>
+    <t>zu7</t>
+  </si>
+  <si>
+    <t>zai7</t>
+  </si>
+  <si>
+    <t>phoo1</t>
+  </si>
+  <si>
+    <t>sat4</t>
+  </si>
+  <si>
+    <t>hang5</t>
+  </si>
+  <si>
+    <t>cim1</t>
+  </si>
+  <si>
+    <t>jiok8</t>
+  </si>
+  <si>
+    <t>pho1</t>
+  </si>
+  <si>
+    <t>lo5</t>
+  </si>
+  <si>
+    <t>bit8</t>
+  </si>
+  <si>
+    <t>to1</t>
+  </si>
+  <si>
+    <t>si5</t>
+  </si>
+  <si>
+    <t>ziau3</t>
+  </si>
+  <si>
+    <t>kian3</t>
+  </si>
+  <si>
+    <t>ngoo2</t>
+  </si>
+  <si>
+    <t>un3</t>
+  </si>
+  <si>
+    <t>kai1</t>
+  </si>
+  <si>
+    <t>khong1</t>
+  </si>
+  <si>
+    <t>too7</t>
+  </si>
+  <si>
+    <t>it4</t>
+  </si>
+  <si>
+    <t>ce3</t>
+  </si>
+  <si>
+    <t>khoo2</t>
+  </si>
+  <si>
+    <t>eeh4</t>
+  </si>
+  <si>
+    <t>sia2</t>
+  </si>
+  <si>
+    <t>li7</t>
+  </si>
+  <si>
+    <t>zu2</t>
+  </si>
+  <si>
+    <t>sik4</t>
+  </si>
+  <si>
+    <t>put4</t>
+  </si>
+  <si>
+    <t>i7</t>
+  </si>
+  <si>
+    <t>zik4</t>
+  </si>
+  <si>
+    <t>si7</t>
+  </si>
+  <si>
+    <t>siu7</t>
+  </si>
+  <si>
+    <t>siong2</t>
+  </si>
+  <si>
+    <t>ik8</t>
+  </si>
+  <si>
+    <t>hok8</t>
+  </si>
+  <si>
+    <t>ju5</t>
+  </si>
+  <si>
+    <t>zu1</t>
+  </si>
+  <si>
+    <t>huat4</t>
+  </si>
+  <si>
+    <t>siong3</t>
+  </si>
+  <si>
+    <t>sing1</t>
+  </si>
+  <si>
+    <t>biat8</t>
+  </si>
+  <si>
+    <t>koo2</t>
+  </si>
+  <si>
+    <t>zing7</t>
+  </si>
+  <si>
+    <t>zing1</t>
+  </si>
+  <si>
+    <t>kiam2</t>
+  </si>
+  <si>
+    <t>koo3</t>
+  </si>
+  <si>
+    <t>tiong1</t>
+  </si>
+  <si>
+    <t>bu5</t>
+  </si>
+  <si>
+    <t>gan2</t>
+  </si>
+  <si>
+    <t>siat8</t>
+  </si>
+  <si>
+    <t>sin1</t>
+  </si>
+  <si>
+    <t>i3</t>
+  </si>
+  <si>
+    <t>hiong1</t>
+  </si>
+  <si>
+    <t>bi7</t>
+  </si>
+  <si>
+    <t>ciok4</t>
+  </si>
+  <si>
+    <t>kai3</t>
+  </si>
+  <si>
+    <t>nai2</t>
+  </si>
+  <si>
+    <t>zi3</t>
+  </si>
+  <si>
+    <t>bing5</t>
+  </si>
+  <si>
+    <t>zin7</t>
+  </si>
+  <si>
+    <t>lo2</t>
+  </si>
+  <si>
+    <t>su2</t>
+  </si>
+  <si>
+    <t>zip8</t>
+  </si>
+  <si>
+    <t>to7</t>
+  </si>
+  <si>
+    <t>ti3</t>
+  </si>
+  <si>
+    <t>tik4</t>
+  </si>
+  <si>
+    <t>i2</t>
+  </si>
+  <si>
+    <t>soo2</t>
+  </si>
+  <si>
+    <t>the5</t>
+  </si>
+  <si>
+    <t>i1</t>
+  </si>
+  <si>
+    <t>sim1</t>
+  </si>
+  <si>
+    <t>kua3</t>
+  </si>
+  <si>
+    <t>gai7</t>
+  </si>
+  <si>
+    <t>iu2</t>
+  </si>
+  <si>
+    <t>khiong2</t>
+  </si>
+  <si>
+    <t>poo3</t>
+  </si>
+  <si>
+    <t>uan2</t>
+  </si>
+  <si>
+    <t>tian1</t>
+  </si>
+  <si>
+    <t>to3</t>
+  </si>
+  <si>
+    <t>bang7</t>
+  </si>
+  <si>
+    <t>kiu3</t>
+  </si>
+  <si>
+    <t>king3</t>
+  </si>
+  <si>
+    <t>liap4</t>
+  </si>
+  <si>
+    <t>puan5</t>
+  </si>
+  <si>
+    <t>sam1</t>
+  </si>
+  <si>
+    <t>se3</t>
+  </si>
+  <si>
+    <t>hut8</t>
+  </si>
+  <si>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>loo7</t>
+  </si>
+  <si>
+    <t>biau2</t>
+  </si>
+  <si>
+    <t>ti1</t>
+  </si>
+  <si>
+    <t>tai7</t>
+  </si>
+  <si>
+    <t>sin5</t>
+  </si>
+  <si>
+    <t>ziu3</t>
+  </si>
+  <si>
+    <t>ting2</t>
+  </si>
+  <si>
+    <t>ling5</t>
+  </si>
+  <si>
+    <t>tu5</t>
+  </si>
+  <si>
+    <t>zin1</t>
+  </si>
+  <si>
+    <t>sit8</t>
+  </si>
+  <si>
+    <t>hi1</t>
+  </si>
+  <si>
+    <t>suat4</t>
+  </si>
+  <si>
+    <t>uat8</t>
+  </si>
+  <si>
+    <t>te3</t>
+  </si>
+  <si>
+    <t>po5</t>
+  </si>
+  <si>
+    <t>o1</t>
+  </si>
+  <si>
+    <t>kuan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>guan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zai6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phoo1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poo1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sat7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cim1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puan1</t>
+  </si>
+  <si>
+    <t>puan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buan1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>jiok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zziok8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pho1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>po1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lo5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bit8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbit8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>do1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziau3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziao5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kian3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gian5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ngoo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ggnoo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>un3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>un5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gai1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>too7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doo6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>it7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ce3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ce5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khoo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>koo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eh7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sia2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sia3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>le7</t>
+  </si>
+  <si>
+    <t>zu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sik7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>put4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>but7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zik7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>si6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siu6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ik8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ju5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zzu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zu1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>huat7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siong5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbiat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>koo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zing1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiam2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giam3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goo5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>diong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbu2</t>
+  </si>
+  <si>
+    <t>bbu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ggan3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ni2</t>
+  </si>
+  <si>
+    <t>ni2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lni3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pi7</t>
+  </si>
+  <si>
+    <t>pi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bi6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>siat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hiong1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bi7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbi6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ciok4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ciok7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gai5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nai2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lnai3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zi5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbing2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>su2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zip8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>do6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>di5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tik4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dik7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>the5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>te2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kua3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gua5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gai7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ggai6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>iu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khiong2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiong3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poo3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boo5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uan3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>li7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>li6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dian1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>to3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>do5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bang7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbang6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>giu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ging5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>puan5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buan2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sam1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>se5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hut8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loo7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>loo6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biau2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bbiao3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ti1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>di1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dai6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziu3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ziu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ting2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ding3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ling2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tu5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>du2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sit8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hi1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suat7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uat8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>khiat4</t>
+  </si>
+  <si>
+    <t>khiat4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kiat7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>de5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>po5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bo2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>漢字</t>
+  </si>
+  <si>
+    <t>總數</t>
+  </si>
+  <si>
+    <t>台語音標</t>
+  </si>
+  <si>
+    <t>校正音標</t>
+  </si>
+  <si>
+    <t>座標</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>(5, 4)</t>
+  </si>
+  <si>
+    <t>(5, 5)</t>
+  </si>
+  <si>
+    <t>(5, 6)</t>
+  </si>
+  <si>
+    <t>(5, 7); (73, 8); (97, 11); (129, 6)</t>
+  </si>
+  <si>
+    <t>(5, 8); (73, 10); (129, 8)</t>
+  </si>
+  <si>
+    <t>(5, 10); (21, 15); (41, 9)</t>
+  </si>
+  <si>
+    <t>(5, 11)</t>
+  </si>
+  <si>
+    <t>(5, 12); (73, 14); (93, 10); (105, 6); (121, 6)</t>
+  </si>
+  <si>
+    <t>(5, 13); (73, 15); (93, 11); (105, 7); (121, 7)</t>
+  </si>
+  <si>
+    <t>(5, 14); (73, 16); (93, 12); (105, 8); (121, 8); (125, 10); (125, 15)</t>
+  </si>
+  <si>
+    <t>(5, 15); (73, 17); (93, 13); (97, 7); (105, 9); (121, 9); (125, 11); (125, 16)</t>
+  </si>
+  <si>
+    <t>(5, 16); (73, 18); (93, 14); (105, 10); (121, 10)</t>
+  </si>
+  <si>
+    <t>(5, 17); (77, 4); (93, 15); (97, 6); (105, 11); (121, 11)</t>
+  </si>
+  <si>
+    <t>(5, 18)</t>
+  </si>
+  <si>
+    <t>(9, 5)</t>
+  </si>
+  <si>
+    <t>(9, 6)</t>
+  </si>
+  <si>
+    <t>(9, 7)</t>
+  </si>
+  <si>
+    <t>(9, 8)</t>
+  </si>
+  <si>
+    <t>(9, 9)</t>
+  </si>
+  <si>
+    <t>(9, 10); (17, 11); (17, 13); (21, 6); (21, 8); (33, 11); (37, 16)</t>
+  </si>
+  <si>
+    <t>(9, 12)</t>
+  </si>
+  <si>
+    <t>(9, 13); (113, 6)</t>
+  </si>
+  <si>
+    <t>(9, 14); (113, 7)</t>
+  </si>
+  <si>
+    <t>(9, 15); (69, 5); (113, 8)</t>
+  </si>
+  <si>
+    <t>(9, 16)</t>
+  </si>
+  <si>
+    <t>(17, 4); (33, 4)</t>
+  </si>
+  <si>
+    <t>(17, 5); (33, 5)</t>
+  </si>
+  <si>
+    <t>(17, 6); (33, 6)</t>
+  </si>
+  <si>
+    <t>(17, 8); (17, 16); (17, 18); (21, 11); (41, 4); (45, 6)</t>
+  </si>
+  <si>
+    <t>(17, 9); (17, 14); (33, 14); (33, 16); (37, 4); (37, 6); (37, 9); (37, 11); (113, 12)</t>
+  </si>
+  <si>
+    <t>(17, 10); (17, 15)</t>
+  </si>
+  <si>
+    <t>(21, 4); (21, 9); (121, 14)</t>
+  </si>
+  <si>
+    <t>(21, 5); (21, 10); (25, 6); (33, 8); (37, 14); (105, 13); (105, 18); (109, 8); (109, 13)</t>
+  </si>
+  <si>
+    <t>(21, 13); (41, 7)</t>
+  </si>
+  <si>
+    <t>(21, 14); (41, 8); (81, 13)</t>
+  </si>
+  <si>
+    <t>(21, 16); (41, 10); (53, 12)</t>
+  </si>
+  <si>
+    <t>(21, 18); (57, 4); (57, 16); (69, 13)</t>
+  </si>
+  <si>
+    <t>(25, 4)</t>
+  </si>
+  <si>
+    <t>(25, 5)</t>
+  </si>
+  <si>
+    <t>(33, 9); (93, 6)</t>
+  </si>
+  <si>
+    <t>(33, 10); (45, 11)</t>
+  </si>
+  <si>
+    <t>(33, 12)</t>
+  </si>
+  <si>
+    <t>(33, 15)</t>
+  </si>
+  <si>
+    <t>(33, 17); (69, 7)</t>
+  </si>
+  <si>
+    <t>(37, 5)</t>
+  </si>
+  <si>
+    <t>(37, 7)</t>
+  </si>
+  <si>
+    <t>(37, 10)</t>
+  </si>
+  <si>
+    <t>(37, 12)</t>
+  </si>
+  <si>
+    <t>(37, 15); (73, 6); (77, 5); (77, 15); (93, 16); (105, 4); (121, 4)</t>
+  </si>
+  <si>
+    <t>(37, 17)</t>
+  </si>
+  <si>
+    <t>(37, 18); (41, 6); (41, 12); (45, 5); (53, 4); (53, 10); (53, 15); (53, 16); (57, 5); (57, 6); (57, 12); (57, 17); (69, 4); (69, 10); (69, 14); (69, 18); (77, 12); (77, 17); (109, 9); (109, 14)</t>
+  </si>
+  <si>
+    <t>(41, 13); (53, 5)</t>
+  </si>
+  <si>
+    <t>(41, 14)</t>
+  </si>
+  <si>
+    <t>(41, 15)</t>
+  </si>
+  <si>
+    <t>(41, 16)</t>
+  </si>
+  <si>
+    <t>(41, 17)</t>
+  </si>
+  <si>
+    <t>(41, 18); (53, 11)</t>
+  </si>
+  <si>
+    <t>(45, 7)</t>
+  </si>
+  <si>
+    <t>(45, 8)</t>
+  </si>
+  <si>
+    <t>(45, 9)</t>
+  </si>
+  <si>
+    <t>(45, 10)</t>
+  </si>
+  <si>
+    <t>(53, 6); (53, 13)</t>
+  </si>
+  <si>
+    <t>(53, 8); (57, 10)</t>
+  </si>
+  <si>
+    <t>(53, 9); (57, 11)</t>
+  </si>
+  <si>
+    <t>(53, 17); (57, 7); (109, 5)</t>
+  </si>
+  <si>
+    <t>(57, 8); (61, 5)</t>
+  </si>
+  <si>
+    <t>(57, 13); (57, 18)</t>
+  </si>
+  <si>
+    <t>(57, 14); (61, 4)</t>
+  </si>
+  <si>
+    <t>(69, 6)</t>
+  </si>
+  <si>
+    <t>(69, 8)</t>
+  </si>
+  <si>
+    <t>(69, 11)</t>
+  </si>
+  <si>
+    <t>(69, 15); (73, 5); (77, 8); (93, 18)</t>
+  </si>
+  <si>
+    <t>(69, 17)</t>
+  </si>
+  <si>
+    <t>(73, 4)</t>
+  </si>
+  <si>
+    <t>(73, 9); (97, 12); (129, 7)</t>
+  </si>
+  <si>
+    <t>(73, 13); (93, 9)</t>
+  </si>
+  <si>
+    <t>(77, 7)</t>
+  </si>
+  <si>
+    <t>(77, 9); (77, 13)</t>
+  </si>
+  <si>
+    <t>(77, 10); (77, 14)</t>
+  </si>
+  <si>
+    <t>(77, 18)</t>
+  </si>
+  <si>
+    <t>(81, 4)</t>
+  </si>
+  <si>
+    <t>(81, 5)</t>
+  </si>
+  <si>
+    <t>(81, 7)</t>
+  </si>
+  <si>
+    <t>(81, 8)</t>
+  </si>
+  <si>
+    <t>(81, 9)</t>
+  </si>
+  <si>
+    <t>(81, 10)</t>
+  </si>
+  <si>
+    <t>(81, 12)</t>
+  </si>
+  <si>
+    <t>(81, 15)</t>
+  </si>
+  <si>
+    <t>(81, 16)</t>
+  </si>
+  <si>
+    <t>(81, 18)</t>
+  </si>
+  <si>
+    <t>(93, 4); (97, 8); (97, 10)</t>
+  </si>
+  <si>
+    <t>(93, 5)</t>
+  </si>
+  <si>
+    <t>(93, 7)</t>
+  </si>
+  <si>
+    <t>(97, 4)</t>
+  </si>
+  <si>
+    <t>(97, 5)</t>
+  </si>
+  <si>
+    <t>(97, 9)</t>
+  </si>
+  <si>
+    <t>(105, 5)</t>
+  </si>
+  <si>
+    <t>(105, 14); (109, 4)</t>
+  </si>
+  <si>
+    <t>(105, 15)</t>
+  </si>
+  <si>
+    <t>(105, 16); (109, 6); (109, 11); (109, 17); (121, 12); (121, 16)</t>
+  </si>
+  <si>
+    <t>(109, 10)</t>
+  </si>
+  <si>
+    <t>(109, 15); (109, 16)</t>
+  </si>
+  <si>
+    <t>(113, 4)</t>
+  </si>
+  <si>
+    <t>(113, 5)</t>
+  </si>
+  <si>
+    <t>(113, 10)</t>
+  </si>
+  <si>
+    <t>(113, 11)</t>
+  </si>
+  <si>
+    <t>(113, 13)</t>
+  </si>
+  <si>
+    <t>(121, 5); (121, 15)</t>
+  </si>
+  <si>
+    <t>(121, 17)</t>
+  </si>
+  <si>
+    <t>(125, 4); (125, 7); (125, 12); (125, 18)</t>
+  </si>
+  <si>
+    <t>(125, 5); (125, 8); (125, 13); (129, 4)</t>
+  </si>
+  <si>
+    <t>(125, 17)</t>
+  </si>
+  <si>
+    <t>(129, 9)</t>
+  </si>
+  <si>
+    <t>(129, 10)</t>
+  </si>
+  <si>
+    <t>(73, 11)</t>
+  </si>
+  <si>
+    <t>(81, 17)</t>
+  </si>
+  <si>
+    <t>閩拼調號</t>
+  </si>
+  <si>
+    <t>網頁每列字數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>φ</t>
+  </si>
+  <si>
+    <t>hing5</t>
+  </si>
+  <si>
+    <t>hing5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eh4</t>
+  </si>
+  <si>
+    <t>eh4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liap4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>liap7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hing2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>觀自在菩薩，行深般若波羅蜜多時，照見五蘊皆空，度一切苦厄。
 舍利子！色不異空，空不異色，色即是空，空即是色，受想行識，亦復如是。
 舍利子！是諸法空相，不生不滅，不垢不淨，不增不減。是故空中無色，無受想行識。無眼耳鼻舌身意；無色聲香味觸法。
@@ -2664,1450 +4109,6 @@
 三世諸佛，依般若波羅蜜多故，得阿耨多羅三藐三菩提！
 故知般若波羅蜜多，是大神咒，是大明咒，是無上咒，是無等等咒。能除一切苦！真實不虛！
 故說般若波羅蜜多咒，即說咒曰：揭諦，揭諦，波羅揭諦，波羅僧揭諦，菩提薩婆訶！</t>
-  </si>
-  <si>
-    <t>無預設</t>
-  </si>
-  <si>
-    <t>kuan1</t>
-  </si>
-  <si>
-    <t>zu7</t>
-  </si>
-  <si>
-    <t>zai7</t>
-  </si>
-  <si>
-    <t>phoo1</t>
-  </si>
-  <si>
-    <t>sat4</t>
-  </si>
-  <si>
-    <t>hang5</t>
-  </si>
-  <si>
-    <t>cim1</t>
-  </si>
-  <si>
-    <t>jiok8</t>
-  </si>
-  <si>
-    <t>pho1</t>
-  </si>
-  <si>
-    <t>lo5</t>
-  </si>
-  <si>
-    <t>bit8</t>
-  </si>
-  <si>
-    <t>to1</t>
-  </si>
-  <si>
-    <t>si5</t>
-  </si>
-  <si>
-    <t>ziau3</t>
-  </si>
-  <si>
-    <t>kian3</t>
-  </si>
-  <si>
-    <t>ngoo2</t>
-  </si>
-  <si>
-    <t>un3</t>
-  </si>
-  <si>
-    <t>kai1</t>
-  </si>
-  <si>
-    <t>khong1</t>
-  </si>
-  <si>
-    <t>too7</t>
-  </si>
-  <si>
-    <t>it4</t>
-  </si>
-  <si>
-    <t>ce3</t>
-  </si>
-  <si>
-    <t>khoo2</t>
-  </si>
-  <si>
-    <t>eeh4</t>
-  </si>
-  <si>
-    <t>sia2</t>
-  </si>
-  <si>
-    <t>li7</t>
-  </si>
-  <si>
-    <t>zu2</t>
-  </si>
-  <si>
-    <t>sik4</t>
-  </si>
-  <si>
-    <t>put4</t>
-  </si>
-  <si>
-    <t>i7</t>
-  </si>
-  <si>
-    <t>zik4</t>
-  </si>
-  <si>
-    <t>si7</t>
-  </si>
-  <si>
-    <t>siu7</t>
-  </si>
-  <si>
-    <t>siong2</t>
-  </si>
-  <si>
-    <t>ik8</t>
-  </si>
-  <si>
-    <t>hok8</t>
-  </si>
-  <si>
-    <t>ju5</t>
-  </si>
-  <si>
-    <t>zu1</t>
-  </si>
-  <si>
-    <t>huat4</t>
-  </si>
-  <si>
-    <t>siong3</t>
-  </si>
-  <si>
-    <t>sing1</t>
-  </si>
-  <si>
-    <t>biat8</t>
-  </si>
-  <si>
-    <t>koo2</t>
-  </si>
-  <si>
-    <t>zing7</t>
-  </si>
-  <si>
-    <t>zing1</t>
-  </si>
-  <si>
-    <t>kiam2</t>
-  </si>
-  <si>
-    <t>koo3</t>
-  </si>
-  <si>
-    <t>tiong1</t>
-  </si>
-  <si>
-    <t>bu5</t>
-  </si>
-  <si>
-    <t>gan2</t>
-  </si>
-  <si>
-    <t>siat8</t>
-  </si>
-  <si>
-    <t>sin1</t>
-  </si>
-  <si>
-    <t>i3</t>
-  </si>
-  <si>
-    <t>hiong1</t>
-  </si>
-  <si>
-    <t>bi7</t>
-  </si>
-  <si>
-    <t>ciok4</t>
-  </si>
-  <si>
-    <t>kai3</t>
-  </si>
-  <si>
-    <t>nai2</t>
-  </si>
-  <si>
-    <t>zi3</t>
-  </si>
-  <si>
-    <t>bing5</t>
-  </si>
-  <si>
-    <t>zin7</t>
-  </si>
-  <si>
-    <t>lo2</t>
-  </si>
-  <si>
-    <t>su2</t>
-  </si>
-  <si>
-    <t>zip8</t>
-  </si>
-  <si>
-    <t>to7</t>
-  </si>
-  <si>
-    <t>ti3</t>
-  </si>
-  <si>
-    <t>tik4</t>
-  </si>
-  <si>
-    <t>i2</t>
-  </si>
-  <si>
-    <t>soo2</t>
-  </si>
-  <si>
-    <t>the5</t>
-  </si>
-  <si>
-    <t>i1</t>
-  </si>
-  <si>
-    <t>sim1</t>
-  </si>
-  <si>
-    <t>kua3</t>
-  </si>
-  <si>
-    <t>gai7</t>
-  </si>
-  <si>
-    <t>iu2</t>
-  </si>
-  <si>
-    <t>khiong2</t>
-  </si>
-  <si>
-    <t>poo3</t>
-  </si>
-  <si>
-    <t>uan2</t>
-  </si>
-  <si>
-    <t>tian1</t>
-  </si>
-  <si>
-    <t>to3</t>
-  </si>
-  <si>
-    <t>bang7</t>
-  </si>
-  <si>
-    <t>kiu3</t>
-  </si>
-  <si>
-    <t>king3</t>
-  </si>
-  <si>
-    <t>liap4</t>
-  </si>
-  <si>
-    <t>puan5</t>
-  </si>
-  <si>
-    <t>sam1</t>
-  </si>
-  <si>
-    <t>se3</t>
-  </si>
-  <si>
-    <t>hut8</t>
-  </si>
-  <si>
-    <t>a1</t>
-  </si>
-  <si>
-    <t>loo7</t>
-  </si>
-  <si>
-    <t>biau2</t>
-  </si>
-  <si>
-    <t>ti1</t>
-  </si>
-  <si>
-    <t>tai7</t>
-  </si>
-  <si>
-    <t>sin5</t>
-  </si>
-  <si>
-    <t>ziu3</t>
-  </si>
-  <si>
-    <t>ting2</t>
-  </si>
-  <si>
-    <t>ling5</t>
-  </si>
-  <si>
-    <t>tu5</t>
-  </si>
-  <si>
-    <t>zin1</t>
-  </si>
-  <si>
-    <t>sit8</t>
-  </si>
-  <si>
-    <t>hi1</t>
-  </si>
-  <si>
-    <t>suat4</t>
-  </si>
-  <si>
-    <t>uat8</t>
-  </si>
-  <si>
-    <t>te3</t>
-  </si>
-  <si>
-    <t>po5</t>
-  </si>
-  <si>
-    <t>o1</t>
-  </si>
-  <si>
-    <t>kuan1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>guan1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zai7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zai6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>phoo1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>poo1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sat7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cim1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>puan1</t>
-  </si>
-  <si>
-    <t>puan1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buan1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>jiok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zziok8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pho1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>po1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lo5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bit8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbit8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>do1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziau3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziao5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kian3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gian5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ngoo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ggnoo3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>un3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>un5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gai1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>too7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>doo6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>it7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ce5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khoo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>koo3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eh7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sia2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sia3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>le7</t>
-  </si>
-  <si>
-    <t>zu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sik7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>put4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>but7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zik7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>si6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siu7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siu6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ik8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ju5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zzu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zu1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>huat7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siong5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>biat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbiat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>koo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goo3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zing7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zing6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zing1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kiam2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>giam3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goo5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tiong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>diong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbu2</t>
-  </si>
-  <si>
-    <t>bbu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gan2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ggan3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ni2</t>
-  </si>
-  <si>
-    <t>ni2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lni3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>pi7</t>
-  </si>
-  <si>
-    <t>pi7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bi6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>siat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hiong1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bi7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbi6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ciok4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ciok7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gai5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nai2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lnai3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zi5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bing5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbing2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lo3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>su2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zip8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>do6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>di5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tik4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dik7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>the5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>te2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sim1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kua3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gua5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gai7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ggai6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iu2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khiong2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kiong3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>poo3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>boo5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uan3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>li7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>li6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tian1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dian1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>do5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bang7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbang6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>giu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ging5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>puan5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>buan2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sam1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>se5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hut8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loo7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loo6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>biau2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bbiao3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ti1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>di1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dai6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sin5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sin2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziu3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ziu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ting2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ding3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ling2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tu5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>du2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zin1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sit8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hi1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>suat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>suat7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>uat8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>khiat4</t>
-  </si>
-  <si>
-    <t>khiat4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kiat7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>de5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>po5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bo2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>漢字</t>
-  </si>
-  <si>
-    <t>總數</t>
-  </si>
-  <si>
-    <t>台語音標</t>
-  </si>
-  <si>
-    <t>校正音標</t>
-  </si>
-  <si>
-    <t>座標</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>(5, 4)</t>
-  </si>
-  <si>
-    <t>(5, 5)</t>
-  </si>
-  <si>
-    <t>(5, 6)</t>
-  </si>
-  <si>
-    <t>(5, 7); (73, 8); (97, 11); (129, 6)</t>
-  </si>
-  <si>
-    <t>(5, 8); (73, 10); (129, 8)</t>
-  </si>
-  <si>
-    <t>(5, 10); (21, 15); (41, 9)</t>
-  </si>
-  <si>
-    <t>(5, 11)</t>
-  </si>
-  <si>
-    <t>(5, 12); (73, 14); (93, 10); (105, 6); (121, 6)</t>
-  </si>
-  <si>
-    <t>(5, 13); (73, 15); (93, 11); (105, 7); (121, 7)</t>
-  </si>
-  <si>
-    <t>(5, 14); (73, 16); (93, 12); (105, 8); (121, 8); (125, 10); (125, 15)</t>
-  </si>
-  <si>
-    <t>(5, 15); (73, 17); (93, 13); (97, 7); (105, 9); (121, 9); (125, 11); (125, 16)</t>
-  </si>
-  <si>
-    <t>(5, 16); (73, 18); (93, 14); (105, 10); (121, 10)</t>
-  </si>
-  <si>
-    <t>(5, 17); (77, 4); (93, 15); (97, 6); (105, 11); (121, 11)</t>
-  </si>
-  <si>
-    <t>(5, 18)</t>
-  </si>
-  <si>
-    <t>(9, 5)</t>
-  </si>
-  <si>
-    <t>(9, 6)</t>
-  </si>
-  <si>
-    <t>(9, 7)</t>
-  </si>
-  <si>
-    <t>(9, 8)</t>
-  </si>
-  <si>
-    <t>(9, 9)</t>
-  </si>
-  <si>
-    <t>(9, 10); (17, 11); (17, 13); (21, 6); (21, 8); (33, 11); (37, 16)</t>
-  </si>
-  <si>
-    <t>(9, 12)</t>
-  </si>
-  <si>
-    <t>(9, 13); (113, 6)</t>
-  </si>
-  <si>
-    <t>(9, 14); (113, 7)</t>
-  </si>
-  <si>
-    <t>(9, 15); (69, 5); (113, 8)</t>
-  </si>
-  <si>
-    <t>(9, 16)</t>
-  </si>
-  <si>
-    <t>(17, 4); (33, 4)</t>
-  </si>
-  <si>
-    <t>(17, 5); (33, 5)</t>
-  </si>
-  <si>
-    <t>(17, 6); (33, 6)</t>
-  </si>
-  <si>
-    <t>(17, 8); (17, 16); (17, 18); (21, 11); (41, 4); (45, 6)</t>
-  </si>
-  <si>
-    <t>(17, 9); (17, 14); (33, 14); (33, 16); (37, 4); (37, 6); (37, 9); (37, 11); (113, 12)</t>
-  </si>
-  <si>
-    <t>(17, 10); (17, 15)</t>
-  </si>
-  <si>
-    <t>(21, 4); (21, 9); (121, 14)</t>
-  </si>
-  <si>
-    <t>(21, 5); (21, 10); (25, 6); (33, 8); (37, 14); (105, 13); (105, 18); (109, 8); (109, 13)</t>
-  </si>
-  <si>
-    <t>(21, 13); (41, 7)</t>
-  </si>
-  <si>
-    <t>(21, 14); (41, 8); (81, 13)</t>
-  </si>
-  <si>
-    <t>(21, 16); (41, 10); (53, 12)</t>
-  </si>
-  <si>
-    <t>(21, 18); (57, 4); (57, 16); (69, 13)</t>
-  </si>
-  <si>
-    <t>(25, 4)</t>
-  </si>
-  <si>
-    <t>(25, 5)</t>
-  </si>
-  <si>
-    <t>(33, 9); (93, 6)</t>
-  </si>
-  <si>
-    <t>(33, 10); (45, 11)</t>
-  </si>
-  <si>
-    <t>(33, 12)</t>
-  </si>
-  <si>
-    <t>(33, 15)</t>
-  </si>
-  <si>
-    <t>(33, 17); (69, 7)</t>
-  </si>
-  <si>
-    <t>(37, 5)</t>
-  </si>
-  <si>
-    <t>(37, 7)</t>
-  </si>
-  <si>
-    <t>(37, 10)</t>
-  </si>
-  <si>
-    <t>(37, 12)</t>
-  </si>
-  <si>
-    <t>(37, 15); (73, 6); (77, 5); (77, 15); (93, 16); (105, 4); (121, 4)</t>
-  </si>
-  <si>
-    <t>(37, 17)</t>
-  </si>
-  <si>
-    <t>(37, 18); (41, 6); (41, 12); (45, 5); (53, 4); (53, 10); (53, 15); (53, 16); (57, 5); (57, 6); (57, 12); (57, 17); (69, 4); (69, 10); (69, 14); (69, 18); (77, 12); (77, 17); (109, 9); (109, 14)</t>
-  </si>
-  <si>
-    <t>(41, 13); (53, 5)</t>
-  </si>
-  <si>
-    <t>(41, 14)</t>
-  </si>
-  <si>
-    <t>(41, 15)</t>
-  </si>
-  <si>
-    <t>(41, 16)</t>
-  </si>
-  <si>
-    <t>(41, 17)</t>
-  </si>
-  <si>
-    <t>(41, 18); (53, 11)</t>
-  </si>
-  <si>
-    <t>(45, 7)</t>
-  </si>
-  <si>
-    <t>(45, 8)</t>
-  </si>
-  <si>
-    <t>(45, 9)</t>
-  </si>
-  <si>
-    <t>(45, 10)</t>
-  </si>
-  <si>
-    <t>(53, 6); (53, 13)</t>
-  </si>
-  <si>
-    <t>(53, 8); (57, 10)</t>
-  </si>
-  <si>
-    <t>(53, 9); (57, 11)</t>
-  </si>
-  <si>
-    <t>(53, 17); (57, 7); (109, 5)</t>
-  </si>
-  <si>
-    <t>(57, 8); (61, 5)</t>
-  </si>
-  <si>
-    <t>(57, 13); (57, 18)</t>
-  </si>
-  <si>
-    <t>(57, 14); (61, 4)</t>
-  </si>
-  <si>
-    <t>(69, 6)</t>
-  </si>
-  <si>
-    <t>(69, 8)</t>
-  </si>
-  <si>
-    <t>(69, 11)</t>
-  </si>
-  <si>
-    <t>(69, 15); (73, 5); (77, 8); (93, 18)</t>
-  </si>
-  <si>
-    <t>(69, 17)</t>
-  </si>
-  <si>
-    <t>(73, 4)</t>
-  </si>
-  <si>
-    <t>(73, 9); (97, 12); (129, 7)</t>
-  </si>
-  <si>
-    <t>(73, 13); (93, 9)</t>
-  </si>
-  <si>
-    <t>(77, 7)</t>
-  </si>
-  <si>
-    <t>(77, 9); (77, 13)</t>
-  </si>
-  <si>
-    <t>(77, 10); (77, 14)</t>
-  </si>
-  <si>
-    <t>(77, 18)</t>
-  </si>
-  <si>
-    <t>(81, 4)</t>
-  </si>
-  <si>
-    <t>(81, 5)</t>
-  </si>
-  <si>
-    <t>(81, 7)</t>
-  </si>
-  <si>
-    <t>(81, 8)</t>
-  </si>
-  <si>
-    <t>(81, 9)</t>
-  </si>
-  <si>
-    <t>(81, 10)</t>
-  </si>
-  <si>
-    <t>(81, 12)</t>
-  </si>
-  <si>
-    <t>(81, 15)</t>
-  </si>
-  <si>
-    <t>(81, 16)</t>
-  </si>
-  <si>
-    <t>(81, 18)</t>
-  </si>
-  <si>
-    <t>(93, 4); (97, 8); (97, 10)</t>
-  </si>
-  <si>
-    <t>(93, 5)</t>
-  </si>
-  <si>
-    <t>(93, 7)</t>
-  </si>
-  <si>
-    <t>(97, 4)</t>
-  </si>
-  <si>
-    <t>(97, 5)</t>
-  </si>
-  <si>
-    <t>(97, 9)</t>
-  </si>
-  <si>
-    <t>(105, 5)</t>
-  </si>
-  <si>
-    <t>(105, 14); (109, 4)</t>
-  </si>
-  <si>
-    <t>(105, 15)</t>
-  </si>
-  <si>
-    <t>(105, 16); (109, 6); (109, 11); (109, 17); (121, 12); (121, 16)</t>
-  </si>
-  <si>
-    <t>(109, 10)</t>
-  </si>
-  <si>
-    <t>(109, 15); (109, 16)</t>
-  </si>
-  <si>
-    <t>(113, 4)</t>
-  </si>
-  <si>
-    <t>(113, 5)</t>
-  </si>
-  <si>
-    <t>(113, 10)</t>
-  </si>
-  <si>
-    <t>(113, 11)</t>
-  </si>
-  <si>
-    <t>(113, 13)</t>
-  </si>
-  <si>
-    <t>(121, 5); (121, 15)</t>
-  </si>
-  <si>
-    <t>(121, 17)</t>
-  </si>
-  <si>
-    <t>(125, 4); (125, 7); (125, 12); (125, 18)</t>
-  </si>
-  <si>
-    <t>(125, 5); (125, 8); (125, 13); (129, 4)</t>
-  </si>
-  <si>
-    <t>(125, 17)</t>
-  </si>
-  <si>
-    <t>(129, 9)</t>
-  </si>
-  <si>
-    <t>(129, 10)</t>
-  </si>
-  <si>
-    <t>(73, 11)</t>
-  </si>
-  <si>
-    <t>(81, 17)</t>
-  </si>
-  <si>
-    <t>閩拼調號</t>
-  </si>
-  <si>
-    <t>網頁每列字數</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>φ</t>
-  </si>
-  <si>
-    <t>hing5</t>
-  </si>
-  <si>
-    <t>hing5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eh4</t>
-  </si>
-  <si>
-    <t>eh4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liap4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>liap7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hing2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5244,6 +5245,9 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="77" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="82" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -5260,9 +5264,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="77" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8202,7 +8203,7 @@
         <v>321</v>
       </c>
       <c r="C13" s="104" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="30">
@@ -8210,7 +8211,7 @@
         <v>322</v>
       </c>
       <c r="C14" s="104" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="30">
@@ -8226,7 +8227,7 @@
         <v>655</v>
       </c>
       <c r="C16" s="104" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="30">
@@ -8239,7 +8240,7 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="53" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C18" s="107">
         <v>7</v>
@@ -8805,19 +8806,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1" t="s">
         <v>950</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>951</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>952</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>953</v>
-      </c>
-      <c r="E1" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8828,13 +8829,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8845,13 +8846,13 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
   </sheetData>
@@ -8867,19 +8868,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1" t="s">
         <v>950</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>951</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>952</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>953</v>
-      </c>
-      <c r="E1" t="s">
-        <v>954</v>
       </c>
     </row>
   </sheetData>
@@ -8895,19 +8896,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1" t="s">
         <v>950</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>951</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>952</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>953</v>
-      </c>
-      <c r="E1" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -8918,13 +8919,13 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D2" t="s">
+        <v>954</v>
+      </c>
+      <c r="E2" t="s">
         <v>955</v>
-      </c>
-      <c r="E2" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -8935,13 +8936,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8952,13 +8953,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -8969,13 +8970,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -8986,13 +8987,13 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D6" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E6" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9003,13 +9004,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D7" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9020,13 +9021,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D8" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9037,13 +9038,13 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D9" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E9" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9054,13 +9055,13 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D10" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E10" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9071,13 +9072,13 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D11" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E11" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9088,13 +9089,13 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D12" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E12" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9105,13 +9106,13 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D13" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E13" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9122,13 +9123,13 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D14" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E14" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9139,13 +9140,13 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D15" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E15" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9156,13 +9157,13 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D16" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E16" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9173,13 +9174,13 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D17" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E17" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9190,13 +9191,13 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D18" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E18" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9207,13 +9208,13 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D19" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E19" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9224,13 +9225,13 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D20" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E20" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9241,13 +9242,13 @@
         <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D21" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E21" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9258,13 +9259,13 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D22" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E22" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9275,13 +9276,13 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D23" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E23" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9292,13 +9293,13 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D24" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E24" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9309,13 +9310,13 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D25" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E25" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9326,13 +9327,13 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D26" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9343,13 +9344,13 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D27" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E27" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9360,13 +9361,13 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D28" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E28" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9377,13 +9378,13 @@
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D29" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E29" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9394,13 +9395,13 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D30" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E30" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9411,13 +9412,13 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D31" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E31" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9428,13 +9429,13 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D32" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E32" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9445,13 +9446,13 @@
         <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D33" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E33" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9462,13 +9463,13 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D34" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E34" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9479,13 +9480,13 @@
         <v>2</v>
       </c>
       <c r="C35" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D35" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E35" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9496,13 +9497,13 @@
         <v>3</v>
       </c>
       <c r="C36" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D36" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E36" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9513,13 +9514,13 @@
         <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D37" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E37" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9530,13 +9531,13 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D38" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E38" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9547,13 +9548,13 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D39" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E39" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9564,13 +9565,13 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D40" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E40" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9581,13 +9582,13 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D41" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E41" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -9598,13 +9599,13 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D42" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E42" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -9615,13 +9616,13 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D43" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E43" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -9632,13 +9633,13 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D44" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E44" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -9649,13 +9650,13 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D45" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E45" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9666,13 +9667,13 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D46" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E46" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -9683,13 +9684,13 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D47" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E47" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -9700,13 +9701,13 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D48" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E48" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -9717,13 +9718,13 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D49" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E49" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9734,13 +9735,13 @@
         <v>7</v>
       </c>
       <c r="C50" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D50" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E50" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9751,13 +9752,13 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D51" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E51" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -9768,13 +9769,13 @@
         <v>20</v>
       </c>
       <c r="C52" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D52" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E52" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -9785,13 +9786,13 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D53" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E53" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -9802,13 +9803,13 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D54" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E54" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -9819,13 +9820,13 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D55" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E55" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -9836,13 +9837,13 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D56" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E56" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -9853,13 +9854,13 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D57" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E57" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -9870,13 +9871,13 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D58" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E58" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -9887,13 +9888,13 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D59" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E59" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -9904,13 +9905,13 @@
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D60" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E60" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -9921,13 +9922,13 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D61" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E61" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -9938,13 +9939,13 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D62" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E62" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -9955,13 +9956,13 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D63" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E63" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -9972,13 +9973,13 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D64" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E64" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -9989,13 +9990,13 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D65" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E65" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -10006,13 +10007,13 @@
         <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D66" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E66" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -10023,13 +10024,13 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D67" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E67" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -10040,13 +10041,13 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D68" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E68" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -10057,13 +10058,13 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D69" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E69" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -10074,13 +10075,13 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D70" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E70" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -10091,13 +10092,13 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D71" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E71" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -10108,13 +10109,13 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D72" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E72" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -10125,13 +10126,13 @@
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D73" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E73" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -10142,13 +10143,13 @@
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D74" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E74" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -10159,13 +10160,13 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D75" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E75" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -10176,13 +10177,13 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D76" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E76" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -10193,13 +10194,13 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D77" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E77" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -10210,13 +10211,13 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D78" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E78" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -10227,13 +10228,13 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D79" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E79" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -10244,13 +10245,13 @@
         <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D80" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E80" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -10261,13 +10262,13 @@
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D81" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E81" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -10278,13 +10279,13 @@
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D82" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -10295,13 +10296,13 @@
         <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D83" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E83" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -10312,13 +10313,13 @@
         <v>1</v>
       </c>
       <c r="C84" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D84" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E84" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -10329,13 +10330,13 @@
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D85" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E85" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -10346,13 +10347,13 @@
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D86" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E86" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -10363,13 +10364,13 @@
         <v>1</v>
       </c>
       <c r="C87" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D87" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E87" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -10380,13 +10381,13 @@
         <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D88" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E88" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -10397,13 +10398,13 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D89" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E89" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -10414,13 +10415,13 @@
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D90" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E90" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -10431,13 +10432,13 @@
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D91" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E91" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -10448,13 +10449,13 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D92" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E92" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -10465,13 +10466,13 @@
         <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D93" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E93" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -10482,13 +10483,13 @@
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D94" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E94" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -10499,13 +10500,13 @@
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D95" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E95" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -10516,13 +10517,13 @@
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D96" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E96" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -10533,13 +10534,13 @@
         <v>1</v>
       </c>
       <c r="C97" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D97" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E97" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -10550,13 +10551,13 @@
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D98" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E98" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -10567,13 +10568,13 @@
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D99" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E99" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -10584,13 +10585,13 @@
         <v>1</v>
       </c>
       <c r="C100" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D100" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E100" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -10601,13 +10602,13 @@
         <v>6</v>
       </c>
       <c r="C101" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D101" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E101" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -10618,13 +10619,13 @@
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D102" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E102" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -10635,13 +10636,13 @@
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D103" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E103" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -10652,13 +10653,13 @@
         <v>1</v>
       </c>
       <c r="C104" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D104" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E104" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -10669,13 +10670,13 @@
         <v>1</v>
       </c>
       <c r="C105" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D105" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E105" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -10686,13 +10687,13 @@
         <v>1</v>
       </c>
       <c r="C106" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D106" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E106" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -10703,13 +10704,13 @@
         <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D107" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E107" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -10720,13 +10721,13 @@
         <v>1</v>
       </c>
       <c r="C108" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D108" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E108" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -10737,13 +10738,13 @@
         <v>2</v>
       </c>
       <c r="C109" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D109" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E109" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -10754,13 +10755,13 @@
         <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D110" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E110" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -10771,13 +10772,13 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D111" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E111" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -10788,13 +10789,13 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D112" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E112" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -10805,13 +10806,13 @@
         <v>1</v>
       </c>
       <c r="C113" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D113" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E113" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -10822,13 +10823,13 @@
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D114" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E114" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -10839,13 +10840,13 @@
         <v>1</v>
       </c>
       <c r="C115" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D115" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E115" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
   </sheetData>
@@ -10976,7 +10977,7 @@
       <c r="H3" s="81"/>
       <c r="I3" s="81"/>
       <c r="J3" s="81" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K3" s="81"/>
       <c r="L3" s="81"/>
@@ -10987,57 +10988,57 @@
       <c r="Q3" s="81"/>
       <c r="R3" s="81"/>
       <c r="T3" s="90"/>
-      <c r="V3" s="108" t="s">
-        <v>660</v>
+      <c r="V3" s="109" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B4" s="56"/>
       <c r="D4" s="82" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E4" s="82" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="F4" s="82" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G4" s="82" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H4" s="82" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I4" s="82"/>
       <c r="J4" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="K4" s="82" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L4" s="82" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="M4" s="82" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="N4" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="O4" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="P4" s="82" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Q4" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="R4" s="82" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="S4" s="91"/>
-      <c r="V4" s="109"/>
+      <c r="V4" s="110"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -11061,7 +11062,7 @@
       <c r="I5" s="97" t="s">
         <v>183</v>
       </c>
-      <c r="J5" s="114" t="s">
+      <c r="J5" s="108" t="s">
         <v>594</v>
       </c>
       <c r="K5" s="97" t="s">
@@ -11089,56 +11090,56 @@
         <v>596</v>
       </c>
       <c r="S5" s="92"/>
-      <c r="V5" s="109"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="1:22" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
       <c r="C6" s="85"/>
       <c r="D6" s="83" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E6" s="83" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F6" s="83" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G6" s="83" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H6" s="83" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="I6" s="83"/>
       <c r="J6" s="83" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="K6" s="83" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L6" s="83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="M6" s="83" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="N6" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="O6" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="P6" s="83" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="Q6" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="R6" s="83" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="S6" s="93"/>
-      <c r="V6" s="109"/>
+      <c r="V6" s="110"/>
     </row>
     <row r="7" spans="1:22" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -11156,54 +11157,54 @@
       <c r="N7" s="81"/>
       <c r="O7" s="81"/>
       <c r="P7" s="81" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="Q7" s="81"/>
       <c r="R7" s="81"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="109"/>
+      <c r="V7" s="110"/>
     </row>
     <row r="8" spans="1:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
       <c r="D8" s="82"/>
       <c r="E8" s="82" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F8" s="82" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G8" s="82" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H8" s="82" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="I8" s="82" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="J8" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="K8" s="82"/>
       <c r="L8" s="82" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M8" s="82" t="s">
         <v>263</v>
       </c>
       <c r="N8" s="82" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="O8" s="82" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="P8" s="82" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="Q8" s="82"/>
       <c r="R8" s="82"/>
       <c r="S8" s="91"/>
-      <c r="V8" s="109"/>
+      <c r="V8" s="110"/>
     </row>
     <row r="9" spans="1:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -11246,7 +11247,7 @@
       <c r="O9" s="97" t="s">
         <v>605</v>
       </c>
-      <c r="P9" s="114" t="s">
+      <c r="P9" s="108" t="s">
         <v>606</v>
       </c>
       <c r="Q9" s="97" t="s">
@@ -11259,49 +11260,49 @@
       </c>
       <c r="S9" s="92"/>
       <c r="T9" s="90"/>
-      <c r="V9" s="109"/>
+      <c r="V9" s="110"/>
     </row>
     <row r="10" spans="1:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
       <c r="D10" s="83"/>
       <c r="E10" s="83" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F10" s="83" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G10" s="83" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H10" s="83" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="I10" s="83" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="J10" s="83" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="K10" s="83"/>
       <c r="L10" s="83" t="s">
+        <v>806</v>
+      </c>
+      <c r="M10" s="83" t="s">
         <v>807</v>
       </c>
-      <c r="M10" s="83" t="s">
-        <v>808</v>
-      </c>
       <c r="N10" s="103" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="O10" s="83" t="s">
+        <v>811</v>
+      </c>
+      <c r="P10" s="83" t="s">
         <v>812</v>
-      </c>
-      <c r="P10" s="83" t="s">
-        <v>813</v>
       </c>
       <c r="Q10" s="83"/>
       <c r="R10" s="83"/>
       <c r="S10" s="94"/>
-      <c r="V10" s="109"/>
+      <c r="V10" s="110"/>
     </row>
     <row r="11" spans="1:22" s="66" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="65"/>
@@ -11321,7 +11322,7 @@
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
-      <c r="V11" s="109"/>
+      <c r="V11" s="110"/>
     </row>
     <row r="12" spans="1:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
@@ -11341,7 +11342,7 @@
       <c r="Q12" s="82"/>
       <c r="R12" s="82"/>
       <c r="S12" s="91"/>
-      <c r="V12" s="109"/>
+      <c r="V12" s="110"/>
     </row>
     <row r="13" spans="1:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -11368,7 +11369,7 @@
       <c r="Q13" s="97"/>
       <c r="R13" s="97"/>
       <c r="S13" s="92"/>
-      <c r="V13" s="109"/>
+      <c r="V13" s="110"/>
     </row>
     <row r="14" spans="1:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
@@ -11388,14 +11389,14 @@
       <c r="Q14" s="83"/>
       <c r="R14" s="83"/>
       <c r="S14" s="94"/>
-      <c r="V14" s="109"/>
+      <c r="V14" s="110"/>
     </row>
     <row r="15" spans="1:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
       <c r="C15" s="88"/>
       <c r="D15" s="81"/>
       <c r="E15" s="81" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F15" s="81"/>
       <c r="G15" s="81"/>
@@ -11410,51 +11411,51 @@
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
       <c r="R15" s="81"/>
-      <c r="V15" s="109"/>
+      <c r="V15" s="110"/>
     </row>
     <row r="16" spans="1:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B16" s="56"/>
       <c r="D16" s="82" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E16" s="82" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F16" s="82" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G16" s="82"/>
       <c r="H16" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I16" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J16" s="82" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="K16" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L16" s="82"/>
       <c r="M16" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N16" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="O16" s="82" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="P16" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="Q16" s="82"/>
       <c r="R16" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="S16" s="91"/>
-      <c r="V16" s="109"/>
+      <c r="V16" s="110"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -11464,7 +11465,7 @@
       <c r="D17" s="97" t="s">
         <v>607</v>
       </c>
-      <c r="E17" s="114" t="s">
+      <c r="E17" s="108" t="s">
         <v>608</v>
       </c>
       <c r="F17" s="97" t="s">
@@ -11507,51 +11508,51 @@
         <v>610</v>
       </c>
       <c r="S17" s="92"/>
-      <c r="V17" s="109"/>
+      <c r="V17" s="110"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
       <c r="D18" s="83" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E18" s="83" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F18" s="83" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G18" s="83"/>
       <c r="H18" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I18" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J18" s="83" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="K18" s="83" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L18" s="83"/>
       <c r="M18" s="83" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N18" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O18" s="83" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="P18" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="Q18" s="83"/>
       <c r="R18" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="S18" s="94"/>
-      <c r="V18" s="109"/>
+      <c r="V18" s="110"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -11571,51 +11572,51 @@
       <c r="P19" s="81"/>
       <c r="Q19" s="81"/>
       <c r="R19" s="81"/>
-      <c r="V19" s="109"/>
+      <c r="V19" s="110"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
       <c r="D20" s="82" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E20" s="82" t="s">
         <v>300</v>
       </c>
       <c r="F20" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G20" s="82"/>
       <c r="H20" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I20" s="82" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J20" s="82" t="s">
         <v>300</v>
       </c>
       <c r="K20" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L20" s="82"/>
       <c r="M20" s="82" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N20" s="82" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="O20" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="P20" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="Q20" s="82"/>
       <c r="R20" s="82" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="S20" s="91"/>
-      <c r="V20" s="109"/>
+      <c r="V20" s="110"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -11655,7 +11656,7 @@
       <c r="N21" s="97" t="s">
         <v>559</v>
       </c>
-      <c r="O21" s="114" t="s">
+      <c r="O21" s="108" t="s">
         <v>594</v>
       </c>
       <c r="P21" s="97" t="s">
@@ -11668,51 +11669,51 @@
         <v>615</v>
       </c>
       <c r="S21" s="92"/>
-      <c r="V21" s="109"/>
+      <c r="V21" s="110"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
       <c r="D22" s="83" t="s">
+        <v>825</v>
+      </c>
+      <c r="E22" s="83" t="s">
         <v>826</v>
       </c>
-      <c r="E22" s="83" t="s">
-        <v>827</v>
-      </c>
       <c r="F22" s="83" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G22" s="83"/>
       <c r="H22" s="83" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="I22" s="83" t="s">
+        <v>825</v>
+      </c>
+      <c r="J22" s="83" t="s">
         <v>826</v>
       </c>
-      <c r="J22" s="83" t="s">
-        <v>827</v>
-      </c>
       <c r="K22" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="L22" s="83"/>
       <c r="M22" s="83" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N22" s="83" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="O22" s="83" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="P22" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="Q22" s="83"/>
       <c r="R22" s="83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="S22" s="94"/>
-      <c r="V22" s="110"/>
+      <c r="V22" s="111"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -11740,7 +11741,7 @@
         <v>281</v>
       </c>
       <c r="E24" s="82" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F24" s="82" t="s">
         <v>300</v>
@@ -11801,10 +11802,10 @@
         <v>281</v>
       </c>
       <c r="E26" s="83" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F26" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G26" s="83"/>
       <c r="H26" s="83"/>
@@ -11955,42 +11956,42 @@
     <row r="32" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B32" s="56"/>
       <c r="D32" s="82" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E32" s="82" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F32" s="82" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G32" s="82"/>
       <c r="H32" s="82" t="s">
         <v>300</v>
       </c>
       <c r="I32" s="82" t="s">
+        <v>834</v>
+      </c>
+      <c r="J32" s="82" t="s">
         <v>835</v>
       </c>
-      <c r="J32" s="82" t="s">
-        <v>836</v>
-      </c>
       <c r="K32" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L32" s="82" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="M32" s="82"/>
       <c r="N32" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="O32" s="82" t="s">
         <v>313</v>
       </c>
       <c r="P32" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q32" s="82" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="R32" s="82"/>
       <c r="S32" s="91"/>
@@ -12008,7 +12009,7 @@
       <c r="D33" s="97" t="s">
         <v>607</v>
       </c>
-      <c r="E33" s="114" t="s">
+      <c r="E33" s="108" t="s">
         <v>608</v>
       </c>
       <c r="F33" s="97" t="s">
@@ -12056,42 +12057,42 @@
     <row r="34" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B34" s="58"/>
       <c r="D34" s="83" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E34" s="83" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F34" s="83" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G34" s="83"/>
       <c r="H34" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I34" s="83" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="J34" s="83" t="s">
+        <v>836</v>
+      </c>
+      <c r="K34" s="83" t="s">
+        <v>804</v>
+      </c>
+      <c r="L34" s="83" t="s">
         <v>837</v>
-      </c>
-      <c r="K34" s="83" t="s">
-        <v>805</v>
-      </c>
-      <c r="L34" s="83" t="s">
-        <v>838</v>
       </c>
       <c r="M34" s="83"/>
       <c r="N34" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O34" s="83" t="s">
         <v>313</v>
       </c>
       <c r="P34" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="Q34" s="83" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R34" s="83"/>
       <c r="S34" s="94"/>
@@ -12120,45 +12121,45 @@
     <row r="36" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B36" s="56"/>
       <c r="D36" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E36" s="82" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F36" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G36" s="82" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H36" s="82"/>
       <c r="I36" s="82" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="J36" s="82" t="s">
+        <v>844</v>
+      </c>
+      <c r="K36" s="82" t="s">
+        <v>820</v>
+      </c>
+      <c r="L36" s="82" t="s">
         <v>845</v>
-      </c>
-      <c r="K36" s="82" t="s">
-        <v>821</v>
-      </c>
-      <c r="L36" s="82" t="s">
-        <v>846</v>
       </c>
       <c r="M36" s="82"/>
       <c r="N36" s="82" t="s">
         <v>300</v>
       </c>
       <c r="O36" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P36" s="82" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="Q36" s="82" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R36" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="S36" s="91"/>
       <c r="V36" s="60"/>
@@ -12219,45 +12220,45 @@
     <row r="38" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B38" s="58"/>
       <c r="D38" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E38" s="83" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F38" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G38" s="83" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H38" s="83"/>
       <c r="I38" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J38" s="83" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K38" s="83" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="L38" s="83" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="M38" s="83"/>
       <c r="N38" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="O38" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="P38" s="83" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="Q38" s="83" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="R38" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="S38" s="94"/>
       <c r="V38" s="60"/>
@@ -12285,45 +12286,45 @@
     <row r="40" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B40" s="56"/>
       <c r="D40" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E40" s="82"/>
       <c r="F40" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G40" s="82" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H40" s="82" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I40" s="82" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="J40" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="K40" s="82"/>
       <c r="L40" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M40" s="82" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N40" s="82" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="O40" s="82" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="P40" s="82" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q40" s="82" t="s">
         <v>862</v>
       </c>
-      <c r="Q40" s="82" t="s">
+      <c r="R40" s="82" t="s">
         <v>863</v>
-      </c>
-      <c r="R40" s="82" t="s">
-        <v>864</v>
       </c>
       <c r="S40" s="91"/>
       <c r="V40" s="60"/>
@@ -12348,7 +12349,7 @@
       <c r="H41" s="97" t="s">
         <v>559</v>
       </c>
-      <c r="I41" s="114" t="s">
+      <c r="I41" s="108" t="s">
         <v>594</v>
       </c>
       <c r="J41" s="97" t="s">
@@ -12384,45 +12385,45 @@
     <row r="42" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B42" s="58"/>
       <c r="D42" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E42" s="83"/>
       <c r="F42" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G42" s="83" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H42" s="83" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I42" s="83" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="J42" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="K42" s="83"/>
       <c r="L42" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M42" s="83" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="N42" s="83" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="O42" s="83" t="s">
+        <v>860</v>
+      </c>
+      <c r="P42" s="83" t="s">
         <v>861</v>
       </c>
-      <c r="P42" s="83" t="s">
+      <c r="Q42" s="83" t="s">
         <v>862</v>
       </c>
-      <c r="Q42" s="83" t="s">
-        <v>863</v>
-      </c>
       <c r="R42" s="83" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="S42" s="94"/>
       <c r="V42" s="60"/>
@@ -12451,25 +12452,25 @@
       <c r="B44" s="56"/>
       <c r="D44" s="82"/>
       <c r="E44" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F44" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G44" s="82" t="s">
         <v>313</v>
       </c>
       <c r="H44" s="82" t="s">
+        <v>865</v>
+      </c>
+      <c r="I44" s="82" t="s">
         <v>866</v>
       </c>
-      <c r="I44" s="82" t="s">
-        <v>867</v>
-      </c>
       <c r="J44" s="82" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K44" s="82" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="L44" s="82"/>
       <c r="M44" s="82"/>
@@ -12530,25 +12531,25 @@
       <c r="B46" s="58"/>
       <c r="D46" s="83"/>
       <c r="E46" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F46" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G46" s="83" t="s">
         <v>313</v>
       </c>
       <c r="H46" s="83" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I46" s="83" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J46" s="83" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K46" s="83" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="L46" s="83"/>
       <c r="M46" s="83"/>
@@ -12670,42 +12671,42 @@
     <row r="52" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B52" s="56"/>
       <c r="D52" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E52" s="82" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F52" s="82" t="s">
         <v>293</v>
       </c>
       <c r="G52" s="82"/>
       <c r="H52" s="82" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="I52" s="82" t="s">
         <v>326</v>
       </c>
       <c r="J52" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K52" s="82" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="L52" s="82" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="M52" s="82" t="s">
         <v>293</v>
       </c>
       <c r="N52" s="82"/>
       <c r="O52" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="P52" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="Q52" s="82" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="R52" s="82"/>
       <c r="S52" s="91"/>
@@ -12767,42 +12768,42 @@
     <row r="54" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B54" s="58"/>
       <c r="D54" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E54" s="83" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F54" s="83" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G54" s="83"/>
       <c r="H54" s="83" t="s">
+        <v>872</v>
+      </c>
+      <c r="I54" s="83" t="s">
         <v>873</v>
       </c>
-      <c r="I54" s="83" t="s">
-        <v>874</v>
-      </c>
       <c r="J54" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K54" s="83" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="L54" s="83" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M54" s="83" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N54" s="83"/>
       <c r="O54" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="P54" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Q54" s="83" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="R54" s="83"/>
       <c r="S54" s="94"/>
@@ -12831,45 +12832,45 @@
     <row r="56" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B56" s="56"/>
       <c r="D56" s="82" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E56" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F56" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G56" s="82" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H56" s="82" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="I56" s="82"/>
       <c r="J56" s="82" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K56" s="82" t="s">
         <v>326</v>
       </c>
       <c r="L56" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M56" s="82" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N56" s="82" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="O56" s="82"/>
       <c r="P56" s="82" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Q56" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R56" s="82" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="S56" s="91"/>
       <c r="V56" s="60"/>
@@ -12930,45 +12931,45 @@
     <row r="58" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B58" s="58"/>
       <c r="D58" s="83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E58" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F58" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G58" s="83" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H58" s="83" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I58" s="83"/>
       <c r="J58" s="83" t="s">
+        <v>872</v>
+      </c>
+      <c r="K58" s="83" t="s">
         <v>873</v>
       </c>
-      <c r="K58" s="83" t="s">
-        <v>874</v>
-      </c>
       <c r="L58" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M58" s="83" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="N58" s="83" t="s">
         <v>290</v>
       </c>
       <c r="O58" s="83"/>
       <c r="P58" s="83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Q58" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R58" s="83" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="S58" s="94"/>
       <c r="V58" s="60"/>
@@ -12996,10 +12997,10 @@
     <row r="60" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B60" s="56"/>
       <c r="D60" s="82" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E60" s="82" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F60" s="82"/>
       <c r="G60" s="82"/>
@@ -13056,7 +13057,7 @@
         <v>290</v>
       </c>
       <c r="E62" s="83" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F62" s="83"/>
       <c r="G62" s="83"/>
@@ -13184,43 +13185,43 @@
     <row r="68" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B68" s="56"/>
       <c r="D68" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E68" s="82" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F68" s="82" t="s">
+        <v>880</v>
+      </c>
+      <c r="G68" s="82" t="s">
+        <v>838</v>
+      </c>
+      <c r="H68" s="82" t="s">
         <v>881</v>
-      </c>
-      <c r="G68" s="82" t="s">
-        <v>839</v>
-      </c>
-      <c r="H68" s="82" t="s">
-        <v>882</v>
       </c>
       <c r="I68" s="82"/>
       <c r="J68" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="K68" s="82" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="L68" s="82"/>
       <c r="M68" s="82" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="N68" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O68" s="82" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="P68" s="82"/>
       <c r="Q68" s="82" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="R68" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="S68" s="91"/>
       <c r="V68" s="60"/>
@@ -13281,43 +13282,43 @@
     <row r="70" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B70" s="58"/>
       <c r="D70" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E70" s="83" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F70" s="83" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G70" s="83" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H70" s="83" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="I70" s="83"/>
       <c r="J70" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K70" s="83" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="L70" s="83"/>
       <c r="M70" s="83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="N70" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O70" s="83" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="P70" s="83"/>
       <c r="Q70" s="83" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="R70" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="S70" s="94"/>
       <c r="V70" s="60"/>
@@ -13348,42 +13349,42 @@
         <v>304</v>
       </c>
       <c r="E72" s="82" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F72" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G72" s="82"/>
       <c r="H72" s="82" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="I72" s="82" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="J72" s="82" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K72" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L72" s="82"/>
       <c r="M72" s="82" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="N72" s="82" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="O72" s="82" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="P72" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="Q72" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="R72" s="82" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="S72" s="91"/>
       <c r="V72" s="60"/>
@@ -13447,42 +13448,42 @@
         <v>292</v>
       </c>
       <c r="E74" s="83" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F74" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G74" s="83"/>
       <c r="H74" s="83" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I74" s="83" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="J74" s="83" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K74" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L74" s="83"/>
       <c r="M74" s="83" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="N74" s="83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="O74" s="83" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P74" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="Q74" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="R74" s="83" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="S74" s="94"/>
       <c r="V74" s="60"/>
@@ -13510,43 +13511,43 @@
     <row r="76" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B76" s="56"/>
       <c r="D76" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E76" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F76" s="82"/>
       <c r="G76" s="82" t="s">
+        <v>891</v>
+      </c>
+      <c r="H76" s="82" t="s">
+        <v>709</v>
+      </c>
+      <c r="I76" s="82" t="s">
         <v>892</v>
       </c>
-      <c r="H76" s="82" t="s">
-        <v>710</v>
-      </c>
-      <c r="I76" s="82" t="s">
-        <v>893</v>
-      </c>
       <c r="J76" s="82" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="K76" s="82"/>
       <c r="L76" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M76" s="82" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N76" s="82" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="O76" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P76" s="82"/>
       <c r="Q76" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="R76" s="82" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="S76" s="91"/>
       <c r="V76" s="60"/>
@@ -13607,43 +13608,43 @@
     <row r="78" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B78" s="58"/>
       <c r="D78" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E78" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F78" s="83"/>
       <c r="G78" s="83" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H78" s="83" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="I78" s="83" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="J78" s="83" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="K78" s="83"/>
       <c r="L78" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M78" s="83" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="N78" s="83" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="O78" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="P78" s="83"/>
       <c r="Q78" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R78" s="83" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="S78" s="94"/>
       <c r="V78" s="60"/>
@@ -13671,30 +13672,30 @@
     <row r="80" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B80" s="56"/>
       <c r="D80" s="82" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E80" s="82" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F80" s="82"/>
       <c r="G80" s="82" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H80" s="82" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="I80" s="82" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="J80" s="82" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="K80" s="82"/>
       <c r="L80" s="82" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="M80" s="82" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N80" s="82"/>
       <c r="O80" s="82" t="s">
@@ -13704,10 +13705,10 @@
         <v>278</v>
       </c>
       <c r="Q80" s="82" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="R80" s="82" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="S80" s="91"/>
       <c r="V80" s="60"/>
@@ -13768,43 +13769,43 @@
     <row r="82" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B82" s="58"/>
       <c r="D82" s="83" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E82" s="83" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F82" s="83"/>
       <c r="G82" s="83" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H82" s="83" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="I82" s="83" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="J82" s="83" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="K82" s="83"/>
       <c r="L82" s="83" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="M82" s="83" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N82" s="83"/>
       <c r="O82" s="83" t="s">
+        <v>912</v>
+      </c>
+      <c r="P82" s="83" t="s">
         <v>913</v>
       </c>
-      <c r="P82" s="83" t="s">
-        <v>914</v>
-      </c>
       <c r="Q82" s="83" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="R82" s="83" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="S82" s="94"/>
       <c r="V82" s="60"/>
@@ -14008,45 +14009,45 @@
     <row r="92" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B92" s="56"/>
       <c r="D92" s="82" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E92" s="82" t="s">
         <v>314</v>
       </c>
       <c r="F92" s="82" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G92" s="82" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H92" s="82"/>
       <c r="I92" s="82" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="J92" s="82" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K92" s="82" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L92" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="M92" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N92" s="82" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="O92" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P92" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q92" s="82"/>
       <c r="R92" s="82" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S92" s="91"/>
       <c r="V92" s="60"/>
@@ -14107,45 +14108,45 @@
     <row r="94" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B94" s="58"/>
       <c r="D94" s="83" t="s">
+        <v>916</v>
+      </c>
+      <c r="E94" s="83" t="s">
         <v>917</v>
       </c>
-      <c r="E94" s="83" t="s">
+      <c r="F94" s="83" t="s">
+        <v>834</v>
+      </c>
+      <c r="G94" s="83" t="s">
         <v>918</v>
-      </c>
-      <c r="F94" s="83" t="s">
-        <v>835</v>
-      </c>
-      <c r="G94" s="83" t="s">
-        <v>919</v>
       </c>
       <c r="H94" s="83"/>
       <c r="I94" s="83" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="J94" s="83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="K94" s="83" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L94" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="M94" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N94" s="83" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="O94" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="P94" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="Q94" s="83"/>
       <c r="R94" s="83" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="S94" s="94"/>
       <c r="V94" s="60"/>
@@ -14173,31 +14174,31 @@
     <row r="96" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B96" s="56"/>
       <c r="D96" s="82" t="s">
+        <v>919</v>
+      </c>
+      <c r="E96" s="82" t="s">
         <v>920</v>
       </c>
-      <c r="E96" s="82" t="s">
-        <v>921</v>
-      </c>
       <c r="F96" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G96" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H96" s="82" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I96" s="82" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J96" s="82" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="K96" s="82" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L96" s="82" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="M96" s="82"/>
       <c r="N96" s="82"/>
@@ -14258,31 +14259,31 @@
     <row r="98" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B98" s="58"/>
       <c r="D98" s="83" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E98" s="83" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F98" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G98" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H98" s="83" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="I98" s="83" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="J98" s="83" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="K98" s="83" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L98" s="83" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="M98" s="83"/>
       <c r="N98" s="83"/>
@@ -14403,28 +14404,28 @@
     <row r="104" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B104" s="56"/>
       <c r="D104" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E104" s="82" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F104" s="82" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G104" s="82" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H104" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="I104" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J104" s="82" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K104" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L104" s="82"/>
       <c r="M104" s="82" t="s">
@@ -14434,10 +14435,10 @@
         <v>310</v>
       </c>
       <c r="O104" s="82" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="P104" s="82" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q104" s="82"/>
       <c r="R104" s="82" t="s">
@@ -14502,45 +14503,45 @@
     <row r="106" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B106" s="58"/>
       <c r="D106" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E106" s="83" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F106" s="83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G106" s="83" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H106" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="I106" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J106" s="83" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K106" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L106" s="83"/>
       <c r="M106" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="N106" s="83" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="O106" s="83" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="P106" s="83" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="Q106" s="83"/>
       <c r="R106" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="S106" s="94"/>
       <c r="V106" s="60"/>
@@ -14571,39 +14572,39 @@
         <v>310</v>
       </c>
       <c r="E108" s="82" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F108" s="82" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G108" s="82"/>
       <c r="H108" s="82" t="s">
         <v>300</v>
       </c>
       <c r="I108" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J108" s="82" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="K108" s="82" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L108" s="82"/>
       <c r="M108" s="82" t="s">
         <v>300</v>
       </c>
       <c r="N108" s="82" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O108" s="82" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="P108" s="82" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="Q108" s="82" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="R108" s="82"/>
       <c r="S108" s="91"/>
@@ -14665,42 +14666,42 @@
     <row r="110" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B110" s="58"/>
       <c r="D110" s="83" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E110" s="83" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F110" s="83" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G110" s="83"/>
       <c r="H110" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="I110" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J110" s="83" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="K110" s="83" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="L110" s="83"/>
       <c r="M110" s="83" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="N110" s="83" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O110" s="83" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="P110" s="83" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="Q110" s="83" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="R110" s="83"/>
       <c r="S110" s="94"/>
@@ -14732,29 +14733,29 @@
         <v>283</v>
       </c>
       <c r="E112" s="82" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F112" s="82" t="s">
         <v>263</v>
       </c>
       <c r="G112" s="82" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H112" s="82" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I112" s="82"/>
       <c r="J112" s="82" t="s">
+        <v>936</v>
+      </c>
+      <c r="K112" s="82" t="s">
         <v>937</v>
       </c>
-      <c r="K112" s="82" t="s">
+      <c r="L112" s="82" t="s">
+        <v>820</v>
+      </c>
+      <c r="M112" s="82" t="s">
         <v>938</v>
-      </c>
-      <c r="L112" s="82" t="s">
-        <v>821</v>
-      </c>
-      <c r="M112" s="82" t="s">
-        <v>939</v>
       </c>
       <c r="N112" s="82"/>
       <c r="O112" s="82"/>
@@ -14816,32 +14817,32 @@
     <row r="114" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B114" s="58"/>
       <c r="D114" s="83" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E114" s="83" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F114" s="83" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G114" s="83" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H114" s="83" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I114" s="83"/>
       <c r="J114" s="83" t="s">
+        <v>936</v>
+      </c>
+      <c r="K114" s="83" t="s">
         <v>937</v>
       </c>
-      <c r="K114" s="83" t="s">
+      <c r="L114" s="83" t="s">
+        <v>821</v>
+      </c>
+      <c r="M114" s="83" t="s">
         <v>938</v>
-      </c>
-      <c r="L114" s="83" t="s">
-        <v>822</v>
-      </c>
-      <c r="M114" s="83" t="s">
-        <v>939</v>
       </c>
       <c r="N114" s="83"/>
       <c r="O114" s="83"/>
@@ -14961,44 +14962,44 @@
     <row r="120" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B120" s="56"/>
       <c r="D120" s="82" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E120" s="82" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F120" s="82" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G120" s="82" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H120" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="I120" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J120" s="82" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K120" s="82" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L120" s="82" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="M120" s="82"/>
       <c r="N120" s="82" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="O120" s="82" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="P120" s="82" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="Q120" s="82" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="R120" s="82"/>
       <c r="S120" s="91"/>
@@ -15060,44 +15061,44 @@
     <row r="122" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B122" s="58"/>
       <c r="D122" s="83" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E122" s="83" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F122" s="83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G122" s="83" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H122" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="I122" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J122" s="83" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K122" s="83" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L122" s="83" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M122" s="83"/>
       <c r="N122" s="83" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="O122" s="83" t="s">
+        <v>940</v>
+      </c>
+      <c r="P122" s="83" t="s">
+        <v>930</v>
+      </c>
+      <c r="Q122" s="83" t="s">
         <v>941</v>
-      </c>
-      <c r="P122" s="83" t="s">
-        <v>931</v>
-      </c>
-      <c r="Q122" s="83" t="s">
-        <v>942</v>
       </c>
       <c r="R122" s="83"/>
       <c r="S122" s="94"/>
@@ -15126,43 +15127,43 @@
     <row r="124" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B124" s="56"/>
       <c r="D124" s="82" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E124" s="82" t="s">
         <v>285</v>
       </c>
       <c r="F124" s="82"/>
       <c r="G124" s="82" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H124" s="82" t="s">
         <v>285</v>
       </c>
       <c r="I124" s="82"/>
       <c r="J124" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K124" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L124" s="82" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="M124" s="82" t="s">
         <v>285</v>
       </c>
       <c r="N124" s="82"/>
       <c r="O124" s="82" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P124" s="82" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="Q124" s="82" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="R124" s="82" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="S124" s="91"/>
       <c r="V124" s="60"/>
@@ -15223,43 +15224,43 @@
     <row r="126" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B126" s="58"/>
       <c r="D126" s="83" t="s">
+        <v>944</v>
+      </c>
+      <c r="E126" s="83" t="s">
         <v>945</v>
-      </c>
-      <c r="E126" s="83" t="s">
-        <v>946</v>
       </c>
       <c r="F126" s="83"/>
       <c r="G126" s="83" t="s">
+        <v>944</v>
+      </c>
+      <c r="H126" s="83" t="s">
         <v>945</v>
-      </c>
-      <c r="H126" s="83" t="s">
-        <v>946</v>
       </c>
       <c r="I126" s="83"/>
       <c r="J126" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="K126" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L126" s="83" t="s">
+        <v>944</v>
+      </c>
+      <c r="M126" s="83" t="s">
         <v>945</v>
-      </c>
-      <c r="M126" s="83" t="s">
-        <v>946</v>
       </c>
       <c r="N126" s="83"/>
       <c r="O126" s="83" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P126" s="83" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="Q126" s="83" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="R126" s="83" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="S126" s="94"/>
       <c r="V126" s="60"/>
@@ -15291,19 +15292,19 @@
       </c>
       <c r="E128" s="82"/>
       <c r="F128" s="82" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G128" s="82" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H128" s="82" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I128" s="82" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="J128" s="82" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="K128" s="82"/>
       <c r="L128" s="82"/>
@@ -15346,7 +15347,7 @@
         <v>609</v>
       </c>
       <c r="L129" s="105" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="M129" s="97"/>
       <c r="N129" s="97"/>
@@ -15360,23 +15361,23 @@
     <row r="130" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B130" s="58"/>
       <c r="D130" s="83" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E130" s="83"/>
       <c r="F130" s="83" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G130" s="83" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H130" s="83" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="I130" s="83" t="s">
+        <v>947</v>
+      </c>
+      <c r="J130" s="83" t="s">
         <v>948</v>
-      </c>
-      <c r="J130" s="83" t="s">
-        <v>949</v>
       </c>
       <c r="K130" s="83"/>
       <c r="L130" s="83"/>
@@ -17898,7 +17899,7 @@
       <c r="Q3" s="81"/>
       <c r="R3" s="81"/>
       <c r="T3" s="90"/>
-      <c r="V3" s="108" t="s">
+      <c r="V3" s="109" t="s">
         <v>205</v>
       </c>
     </row>
@@ -17940,7 +17941,7 @@
       <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
       <c r="S4" s="91"/>
-      <c r="V4" s="109"/>
+      <c r="V4" s="110"/>
     </row>
     <row r="5" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -17982,7 +17983,7 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="97"/>
       <c r="S5" s="92"/>
-      <c r="V5" s="109"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="2:29" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
@@ -18023,7 +18024,7 @@
       <c r="Q6" s="83"/>
       <c r="R6" s="83"/>
       <c r="S6" s="93"/>
-      <c r="V6" s="109"/>
+      <c r="V6" s="110"/>
     </row>
     <row r="7" spans="2:29" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -18044,7 +18045,7 @@
       <c r="Q7" s="81"/>
       <c r="R7" s="81"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="109"/>
+      <c r="V7" s="110"/>
     </row>
     <row r="8" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
@@ -18064,7 +18065,7 @@
       <c r="Q8" s="82"/>
       <c r="R8" s="82"/>
       <c r="S8" s="91"/>
-      <c r="V8" s="109"/>
+      <c r="V8" s="110"/>
     </row>
     <row r="9" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -18088,7 +18089,7 @@
       <c r="R9" s="97"/>
       <c r="S9" s="92"/>
       <c r="T9" s="90"/>
-      <c r="V9" s="109"/>
+      <c r="V9" s="110"/>
     </row>
     <row r="10" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
@@ -18108,7 +18109,7 @@
       <c r="Q10" s="83"/>
       <c r="R10" s="83"/>
       <c r="S10" s="94"/>
-      <c r="V10" s="109"/>
+      <c r="V10" s="110"/>
       <c r="AA10" s="1" t="s">
         <v>182</v>
       </c>
@@ -18133,7 +18134,7 @@
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
-      <c r="V11" s="109"/>
+      <c r="V11" s="110"/>
     </row>
     <row r="12" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
@@ -18177,7 +18178,7 @@
         <v>324</v>
       </c>
       <c r="S12" s="91"/>
-      <c r="V12" s="109"/>
+      <c r="V12" s="110"/>
     </row>
     <row r="13" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -18230,7 +18231,7 @@
         <v>221</v>
       </c>
       <c r="S13" s="92"/>
-      <c r="V13" s="109"/>
+      <c r="V13" s="110"/>
     </row>
     <row r="14" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
@@ -18274,7 +18275,7 @@
         <v>503</v>
       </c>
       <c r="S14" s="94"/>
-      <c r="V14" s="109"/>
+      <c r="V14" s="110"/>
     </row>
     <row r="15" spans="2:29" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -18294,7 +18295,7 @@
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
       <c r="R15" s="81"/>
-      <c r="V15" s="109"/>
+      <c r="V15" s="110"/>
       <c r="AC15" s="67" t="s">
         <v>182</v>
       </c>
@@ -18345,7 +18346,7 @@
         <v>285</v>
       </c>
       <c r="S16" s="91"/>
-      <c r="V16" s="109"/>
+      <c r="V16" s="110"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -18398,7 +18399,7 @@
         <v>226</v>
       </c>
       <c r="S17" s="92"/>
-      <c r="V17" s="109"/>
+      <c r="V17" s="110"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
@@ -18446,7 +18447,7 @@
         <v>508</v>
       </c>
       <c r="S18" s="94"/>
-      <c r="V18" s="109"/>
+      <c r="V18" s="110"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -18470,7 +18471,7 @@
       </c>
       <c r="Q19" s="81"/>
       <c r="R19" s="81"/>
-      <c r="V19" s="109"/>
+      <c r="V19" s="110"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
@@ -18514,7 +18515,7 @@
       </c>
       <c r="R20" s="82"/>
       <c r="S20" s="91"/>
-      <c r="V20" s="109"/>
+      <c r="V20" s="110"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -18567,7 +18568,7 @@
         <v>216</v>
       </c>
       <c r="S21" s="92"/>
-      <c r="V21" s="109"/>
+      <c r="V21" s="110"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
@@ -18611,7 +18612,7 @@
       </c>
       <c r="R22" s="83"/>
       <c r="S22" s="94"/>
-      <c r="V22" s="110"/>
+      <c r="V22" s="111"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -23859,7 +23860,7 @@
       <c r="Q3" s="81"/>
       <c r="R3" s="81"/>
       <c r="T3" s="90"/>
-      <c r="V3" s="108" t="s">
+      <c r="V3" s="109" t="s">
         <v>205</v>
       </c>
     </row>
@@ -23901,7 +23902,7 @@
       <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
       <c r="S4" s="91"/>
-      <c r="V4" s="109"/>
+      <c r="V4" s="110"/>
     </row>
     <row r="5" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -23943,7 +23944,7 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="97"/>
       <c r="S5" s="92"/>
-      <c r="V5" s="109"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="2:29" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
@@ -23984,7 +23985,7 @@
       <c r="Q6" s="83"/>
       <c r="R6" s="83"/>
       <c r="S6" s="93"/>
-      <c r="V6" s="109"/>
+      <c r="V6" s="110"/>
     </row>
     <row r="7" spans="2:29" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -24005,7 +24006,7 @@
       <c r="Q7" s="81"/>
       <c r="R7" s="81"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="109"/>
+      <c r="V7" s="110"/>
     </row>
     <row r="8" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
@@ -24025,7 +24026,7 @@
       <c r="Q8" s="82"/>
       <c r="R8" s="82"/>
       <c r="S8" s="91"/>
-      <c r="V8" s="109"/>
+      <c r="V8" s="110"/>
     </row>
     <row r="9" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -24049,7 +24050,7 @@
       <c r="R9" s="97"/>
       <c r="S9" s="92"/>
       <c r="T9" s="90"/>
-      <c r="V9" s="109"/>
+      <c r="V9" s="110"/>
     </row>
     <row r="10" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
@@ -24069,7 +24070,7 @@
       <c r="Q10" s="83"/>
       <c r="R10" s="83"/>
       <c r="S10" s="94"/>
-      <c r="V10" s="109"/>
+      <c r="V10" s="110"/>
       <c r="AA10" s="1" t="s">
         <v>182</v>
       </c>
@@ -24094,7 +24095,7 @@
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
-      <c r="V11" s="109"/>
+      <c r="V11" s="110"/>
     </row>
     <row r="12" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
@@ -24138,7 +24139,7 @@
         <v>324</v>
       </c>
       <c r="S12" s="91"/>
-      <c r="V12" s="109"/>
+      <c r="V12" s="110"/>
     </row>
     <row r="13" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -24191,7 +24192,7 @@
         <v>221</v>
       </c>
       <c r="S13" s="92"/>
-      <c r="V13" s="109"/>
+      <c r="V13" s="110"/>
     </row>
     <row r="14" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
@@ -24235,7 +24236,7 @@
         <v>354</v>
       </c>
       <c r="S14" s="94"/>
-      <c r="V14" s="109"/>
+      <c r="V14" s="110"/>
     </row>
     <row r="15" spans="2:29" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -24255,7 +24256,7 @@
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
       <c r="R15" s="81"/>
-      <c r="V15" s="109"/>
+      <c r="V15" s="110"/>
       <c r="AC15" s="67" t="s">
         <v>182</v>
       </c>
@@ -24306,7 +24307,7 @@
         <v>285</v>
       </c>
       <c r="S16" s="91"/>
-      <c r="V16" s="109"/>
+      <c r="V16" s="110"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -24359,7 +24360,7 @@
         <v>226</v>
       </c>
       <c r="S17" s="92"/>
-      <c r="V17" s="109"/>
+      <c r="V17" s="110"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
@@ -24407,7 +24408,7 @@
         <v>360</v>
       </c>
       <c r="S18" s="94"/>
-      <c r="V18" s="109"/>
+      <c r="V18" s="110"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -24431,7 +24432,7 @@
       </c>
       <c r="Q19" s="81"/>
       <c r="R19" s="81"/>
-      <c r="V19" s="109"/>
+      <c r="V19" s="110"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
@@ -24475,7 +24476,7 @@
       </c>
       <c r="R20" s="82"/>
       <c r="S20" s="91"/>
-      <c r="V20" s="109"/>
+      <c r="V20" s="110"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -24528,7 +24529,7 @@
         <v>216</v>
       </c>
       <c r="S21" s="92"/>
-      <c r="V21" s="109"/>
+      <c r="V21" s="110"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
@@ -24572,7 +24573,7 @@
       </c>
       <c r="R22" s="83"/>
       <c r="S22" s="94"/>
-      <c r="V22" s="110"/>
+      <c r="V22" s="111"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -29820,7 +29821,7 @@
       <c r="Q3" s="81"/>
       <c r="R3" s="81"/>
       <c r="T3" s="90"/>
-      <c r="V3" s="108" t="s">
+      <c r="V3" s="109" t="s">
         <v>205</v>
       </c>
     </row>
@@ -29862,7 +29863,7 @@
       <c r="Q4" s="82"/>
       <c r="R4" s="82"/>
       <c r="S4" s="91"/>
-      <c r="V4" s="109"/>
+      <c r="V4" s="110"/>
     </row>
     <row r="5" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B5" s="57">
@@ -29904,7 +29905,7 @@
       <c r="Q5" s="97"/>
       <c r="R5" s="97"/>
       <c r="S5" s="92"/>
-      <c r="V5" s="109"/>
+      <c r="V5" s="110"/>
     </row>
     <row r="6" spans="2:29" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="B6" s="58"/>
@@ -29945,7 +29946,7 @@
       <c r="Q6" s="83"/>
       <c r="R6" s="83"/>
       <c r="S6" s="93"/>
-      <c r="V6" s="109"/>
+      <c r="V6" s="110"/>
     </row>
     <row r="7" spans="2:29" s="49" customFormat="1" ht="60" customHeight="1">
       <c r="B7" s="55"/>
@@ -29966,7 +29967,7 @@
       <c r="Q7" s="81"/>
       <c r="R7" s="81"/>
       <c r="S7" s="66"/>
-      <c r="V7" s="109"/>
+      <c r="V7" s="110"/>
     </row>
     <row r="8" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B8" s="56"/>
@@ -29986,7 +29987,7 @@
       <c r="Q8" s="82"/>
       <c r="R8" s="82"/>
       <c r="S8" s="91"/>
-      <c r="V8" s="109"/>
+      <c r="V8" s="110"/>
     </row>
     <row r="9" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B9" s="57">
@@ -30010,7 +30011,7 @@
       <c r="R9" s="97"/>
       <c r="S9" s="92"/>
       <c r="T9" s="90"/>
-      <c r="V9" s="109"/>
+      <c r="V9" s="110"/>
     </row>
     <row r="10" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B10" s="58"/>
@@ -30030,7 +30031,7 @@
       <c r="Q10" s="83"/>
       <c r="R10" s="83"/>
       <c r="S10" s="94"/>
-      <c r="V10" s="109"/>
+      <c r="V10" s="110"/>
     </row>
     <row r="11" spans="2:29" s="66" customFormat="1" ht="60" customHeight="1">
       <c r="B11" s="65"/>
@@ -30052,7 +30053,7 @@
       <c r="P11" s="81"/>
       <c r="Q11" s="81"/>
       <c r="R11" s="81"/>
-      <c r="V11" s="109"/>
+      <c r="V11" s="110"/>
     </row>
     <row r="12" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B12" s="56"/>
@@ -30096,7 +30097,7 @@
         <v>324</v>
       </c>
       <c r="S12" s="91"/>
-      <c r="V12" s="109"/>
+      <c r="V12" s="110"/>
     </row>
     <row r="13" spans="2:29" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B13" s="57">
@@ -30149,7 +30150,7 @@
         <v>221</v>
       </c>
       <c r="S13" s="92"/>
-      <c r="V13" s="109"/>
+      <c r="V13" s="110"/>
     </row>
     <row r="14" spans="2:29" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B14" s="58"/>
@@ -30193,7 +30194,7 @@
         <v>421</v>
       </c>
       <c r="S14" s="94"/>
-      <c r="V14" s="109"/>
+      <c r="V14" s="110"/>
     </row>
     <row r="15" spans="2:29" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B15" s="63"/>
@@ -30213,7 +30214,7 @@
       <c r="P15" s="81"/>
       <c r="Q15" s="81"/>
       <c r="R15" s="81"/>
-      <c r="V15" s="109"/>
+      <c r="V15" s="110"/>
       <c r="AC15" s="67" t="s">
         <v>182</v>
       </c>
@@ -30264,7 +30265,7 @@
         <v>285</v>
       </c>
       <c r="S16" s="91"/>
-      <c r="V16" s="109"/>
+      <c r="V16" s="110"/>
     </row>
     <row r="17" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B17" s="57">
@@ -30317,7 +30318,7 @@
         <v>226</v>
       </c>
       <c r="S17" s="92"/>
-      <c r="V17" s="109"/>
+      <c r="V17" s="110"/>
     </row>
     <row r="18" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B18" s="58"/>
@@ -30365,7 +30366,7 @@
         <v>427</v>
       </c>
       <c r="S18" s="94"/>
-      <c r="V18" s="109"/>
+      <c r="V18" s="110"/>
     </row>
     <row r="19" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B19" s="63"/>
@@ -30387,7 +30388,7 @@
       </c>
       <c r="Q19" s="81"/>
       <c r="R19" s="81"/>
-      <c r="V19" s="109"/>
+      <c r="V19" s="110"/>
     </row>
     <row r="20" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B20" s="56"/>
@@ -30431,7 +30432,7 @@
       </c>
       <c r="R20" s="82"/>
       <c r="S20" s="91"/>
-      <c r="V20" s="109"/>
+      <c r="V20" s="110"/>
     </row>
     <row r="21" spans="2:22" s="1" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="B21" s="57">
@@ -30484,7 +30485,7 @@
         <v>216</v>
       </c>
       <c r="S21" s="92"/>
-      <c r="V21" s="109"/>
+      <c r="V21" s="110"/>
     </row>
     <row r="22" spans="2:22" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="B22" s="58"/>
@@ -30528,7 +30529,7 @@
       </c>
       <c r="R22" s="83"/>
       <c r="S22" s="94"/>
-      <c r="V22" s="110"/>
+      <c r="V22" s="111"/>
     </row>
     <row r="23" spans="2:22" s="67" customFormat="1" ht="60" customHeight="1">
       <c r="B23" s="63"/>
@@ -35767,7 +35768,7 @@
       </c>
     </row>
     <row r="5" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B5" s="111" t="s">
+      <c r="B5" s="112" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -35785,7 +35786,7 @@
       <c r="G5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="111" t="s">
+      <c r="I5" s="112" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -35810,7 +35811,7 @@
       <c r="R5" s="10"/>
     </row>
     <row r="6" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B6" s="112"/>
+      <c r="B6" s="113"/>
       <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
@@ -35830,7 +35831,7 @@
         <f>$B5 &amp; G$4</f>
         <v>陰入</v>
       </c>
-      <c r="I6" s="112"/>
+      <c r="I6" s="113"/>
       <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
@@ -35852,7 +35853,7 @@
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B7" s="112"/>
+      <c r="B7" s="113"/>
       <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
@@ -35868,7 +35869,7 @@
       <c r="G7" s="16">
         <v>30</v>
       </c>
-      <c r="I7" s="112"/>
+      <c r="I7" s="113"/>
       <c r="J7" s="15" t="s">
         <v>22</v>
       </c>
@@ -35890,7 +35891,7 @@
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B8" s="112"/>
+      <c r="B8" s="113"/>
       <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
@@ -35906,7 +35907,7 @@
       <c r="G8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="112"/>
+      <c r="I8" s="113"/>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
@@ -35928,7 +35929,7 @@
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B9" s="112"/>
+      <c r="B9" s="113"/>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
@@ -35944,7 +35945,7 @@
       <c r="G9" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="112"/>
+      <c r="I9" s="113"/>
       <c r="J9" s="11" t="s">
         <v>33</v>
       </c>
@@ -35966,7 +35967,7 @@
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B10" s="113"/>
+      <c r="B10" s="114"/>
       <c r="C10" s="11" t="s">
         <v>38</v>
       </c>
@@ -35982,7 +35983,7 @@
       <c r="G10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="113"/>
+      <c r="I10" s="114"/>
       <c r="J10" s="11" t="s">
         <v>43</v>
       </c>
@@ -36005,7 +36006,7 @@
       <c r="R10" s="28"/>
     </row>
     <row r="11" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B11" s="111" t="s">
+      <c r="B11" s="112" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -36023,7 +36024,7 @@
       <c r="G11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="111" t="s">
+      <c r="I11" s="112" t="s">
         <v>48</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -36047,7 +36048,7 @@
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B12" s="112"/>
+      <c r="B12" s="113"/>
       <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
@@ -36067,7 +36068,7 @@
         <f>$B11 &amp; G$4</f>
         <v>陽入</v>
       </c>
-      <c r="I12" s="112"/>
+      <c r="I12" s="113"/>
       <c r="J12" s="11" t="s">
         <v>17</v>
       </c>
@@ -36087,7 +36088,7 @@
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B13" s="112"/>
+      <c r="B13" s="113"/>
       <c r="C13" s="15" t="s">
         <v>22</v>
       </c>
@@ -36101,7 +36102,7 @@
       <c r="G13" s="16">
         <v>50</v>
       </c>
-      <c r="I13" s="112"/>
+      <c r="I13" s="113"/>
       <c r="J13" s="15" t="s">
         <v>22</v>
       </c>
@@ -36121,7 +36122,7 @@
       <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B14" s="112"/>
+      <c r="B14" s="113"/>
       <c r="C14" s="11" t="s">
         <v>24</v>
       </c>
@@ -36135,7 +36136,7 @@
       <c r="G14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="112"/>
+      <c r="I14" s="113"/>
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
@@ -36155,7 +36156,7 @@
       <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B15" s="112"/>
+      <c r="B15" s="113"/>
       <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
@@ -36169,7 +36170,7 @@
       <c r="G15" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="112"/>
+      <c r="I15" s="113"/>
       <c r="J15" s="11" t="s">
         <v>33</v>
       </c>
@@ -36189,7 +36190,7 @@
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="2:18" ht="36.75" customHeight="1">
-      <c r="B16" s="113"/>
+      <c r="B16" s="114"/>
       <c r="C16" s="11" t="s">
         <v>38</v>
       </c>
@@ -36203,7 +36204,7 @@
       <c r="G16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="I16" s="113"/>
+      <c r="I16" s="114"/>
       <c r="J16" s="11" t="s">
         <v>43</v>
       </c>
